--- a/src/functionalTest/resources/CCD_HRS_v1.8-AAT.xlsx
+++ b/src/functionalTest/resources/CCD_HRS_v1.8-AAT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mustafadayican/hmcts/em/em-hrs-api/src/functionalTest/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A149CB86-60DE-6A4D-A3F6-FB252A5A24F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF320B6-D628-954E-8ADC-A5EFC2982C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20400" tabRatio="500" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8200" yWindow="660" windowWidth="34560" windowHeight="20380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Change History" sheetId="1" r:id="rId1"/>
@@ -24,20 +24,21 @@
     <sheet name="CaseEventToFields" sheetId="9" r:id="rId9"/>
     <sheet name="EventToComplexTypes" sheetId="10" r:id="rId10"/>
     <sheet name="CaseTypeTab" sheetId="11" r:id="rId11"/>
-    <sheet name="ChallengeQuestion" sheetId="12" r:id="rId12"/>
-    <sheet name="SearchInputFields" sheetId="13" r:id="rId13"/>
-    <sheet name="SearchResultFields" sheetId="14" r:id="rId14"/>
-    <sheet name="SearchCaseResultFields" sheetId="15" r:id="rId15"/>
-    <sheet name="WorkBasketInputFields" sheetId="16" r:id="rId16"/>
-    <sheet name="WorkBasketResultFields" sheetId="17" r:id="rId17"/>
-    <sheet name="UserProfile" sheetId="18" r:id="rId18"/>
-    <sheet name="CaseRoles" sheetId="19" r:id="rId19"/>
-    <sheet name="AuthorisationCaseType" sheetId="20" r:id="rId20"/>
-    <sheet name="AuthorisationCaseField" sheetId="21" r:id="rId21"/>
-    <sheet name="AuthorisationCaseEvent" sheetId="22" r:id="rId22"/>
-    <sheet name="AuthorisationCaseState" sheetId="23" r:id="rId23"/>
-    <sheet name="AuthorisationComplexType" sheetId="24" r:id="rId24"/>
-    <sheet name="Banner" sheetId="25" r:id="rId25"/>
+    <sheet name="RoleToAccessProfiles" sheetId="26" r:id="rId12"/>
+    <sheet name="ChallengeQuestion" sheetId="12" r:id="rId13"/>
+    <sheet name="SearchInputFields" sheetId="13" r:id="rId14"/>
+    <sheet name="SearchResultFields" sheetId="14" r:id="rId15"/>
+    <sheet name="SearchCaseResultFields" sheetId="15" r:id="rId16"/>
+    <sheet name="WorkBasketInputFields" sheetId="16" r:id="rId17"/>
+    <sheet name="WorkBasketResultFields" sheetId="17" r:id="rId18"/>
+    <sheet name="UserProfile" sheetId="18" r:id="rId19"/>
+    <sheet name="CaseRoles" sheetId="19" r:id="rId20"/>
+    <sheet name="AuthorisationCaseType" sheetId="20" r:id="rId21"/>
+    <sheet name="AuthorisationCaseField" sheetId="21" r:id="rId22"/>
+    <sheet name="AuthorisationCaseEvent" sheetId="22" r:id="rId23"/>
+    <sheet name="AuthorisationCaseState" sheetId="23" r:id="rId24"/>
+    <sheet name="AuthorisationComplexType" sheetId="24" r:id="rId25"/>
+    <sheet name="Banner" sheetId="25" r:id="rId26"/>
   </sheets>
   <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="361">
   <si>
     <t>Change History</t>
   </si>
@@ -1168,6 +1169,68 @@
   </si>
   <si>
     <t>Add service code to case tab</t>
+  </si>
+  <si>
+    <t>RoleToAccessProfiles</t>
+  </si>
+  <si>
+    <t>Role name from IDAM (prefix idam:) or AM role assignment.
+MaxLength: 100</t>
+  </si>
+  <si>
+    <t>Skill/Authorisation code. Leave blank if no skill filtering needed.</t>
+  </si>
+  <si>
+    <t>Y/N - whether this is read only access</t>
+  </si>
+  <si>
+    <t>Comma separated access profiles to grant.
+MaxLength: 200</t>
+  </si>
+  <si>
+    <t>F = not disabled</t>
+  </si>
+  <si>
+    <t>Optional case access category for skill-based filtering</t>
+  </si>
+  <si>
+    <t>RoleName</t>
+  </si>
+  <si>
+    <t>Authorisation</t>
+  </si>
+  <si>
+    <t>ReadOnly</t>
+  </si>
+  <si>
+    <t>AccessProfiles</t>
+  </si>
+  <si>
+    <t>Disabled</t>
+  </si>
+  <si>
+    <t>CaseAccessCategories</t>
+  </si>
+  <si>
+    <t>idam:caseworker-hrs</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>idam:caseworker-hrs-searcher</t>
+  </si>
+  <si>
+    <t>idam:caseworker-hrs-systemupdate</t>
+  </si>
+  <si>
+    <t>idam:cft-ttl-manager</t>
+  </si>
+  <si>
+    <t>hrs-team-leader</t>
+  </si>
+  <si>
+    <t>Add RoleToAccessProfiles sheet</t>
   </si>
 </sst>
 </file>
@@ -1180,7 +1243,7 @@
     <numFmt numFmtId="166" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="41" x14ac:knownFonts="1">
+  <fonts count="42" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1467,6 +1530,12 @@
       <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1598,7 +1667,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2028,6 +2097,16 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Excel Built-in Explanatory Text" xfId="4" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
@@ -2414,7 +2493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMJ16"/>
+  <dimension ref="A1:AMJ17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.6640625" style="1" customWidth="1"/>
@@ -2632,6 +2711,20 @@
         <v>45960</v>
       </c>
       <c r="D16" s="8" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A17" s="142">
+        <v>1.9</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="C17" s="9">
+        <v>46176</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>314</v>
       </c>
     </row>
@@ -3217,6 +3310,203 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{403AD85A-BCD6-8B44-A8CA-37608B720DFA}">
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="3" max="3" width="33" customWidth="1"/>
+    <col min="4" max="4" width="32.5" customWidth="1"/>
+    <col min="7" max="7" width="44.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="42" x14ac:dyDescent="0.15">
+      <c r="A1" s="151" t="s">
+        <v>341</v>
+      </c>
+      <c r="B1" s="152" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="152" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="152" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="153"/>
+      <c r="F1" s="153"/>
+      <c r="G1" s="153"/>
+      <c r="H1" s="153"/>
+      <c r="I1" s="153"/>
+    </row>
+    <row r="2" spans="1:9" ht="112" x14ac:dyDescent="0.15">
+      <c r="A2" s="152" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="152" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="152" t="s">
+        <v>283</v>
+      </c>
+      <c r="D2" s="152" t="s">
+        <v>342</v>
+      </c>
+      <c r="E2" s="152" t="s">
+        <v>343</v>
+      </c>
+      <c r="F2" s="152" t="s">
+        <v>344</v>
+      </c>
+      <c r="G2" s="152" t="s">
+        <v>345</v>
+      </c>
+      <c r="H2" s="152" t="s">
+        <v>346</v>
+      </c>
+      <c r="I2" s="152" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="42" x14ac:dyDescent="0.15">
+      <c r="A3" s="151" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="151" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="151" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="151" t="s">
+        <v>348</v>
+      </c>
+      <c r="E3" s="151" t="s">
+        <v>349</v>
+      </c>
+      <c r="F3" s="151" t="s">
+        <v>350</v>
+      </c>
+      <c r="G3" s="151" t="s">
+        <v>351</v>
+      </c>
+      <c r="H3" s="151" t="s">
+        <v>352</v>
+      </c>
+      <c r="I3" s="151" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A4" s="154"/>
+      <c r="B4" s="154"/>
+      <c r="C4" s="154" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="154" t="s">
+        <v>354</v>
+      </c>
+      <c r="E4" s="154"/>
+      <c r="F4" s="154" t="s">
+        <v>164</v>
+      </c>
+      <c r="G4" s="154" t="s">
+        <v>287</v>
+      </c>
+      <c r="H4" s="154" t="s">
+        <v>355</v>
+      </c>
+      <c r="I4" s="154"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A5" s="154"/>
+      <c r="B5" s="154"/>
+      <c r="C5" s="154" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="154" t="s">
+        <v>356</v>
+      </c>
+      <c r="E5" s="154"/>
+      <c r="F5" s="154" t="s">
+        <v>164</v>
+      </c>
+      <c r="G5" s="154" t="s">
+        <v>288</v>
+      </c>
+      <c r="H5" s="154" t="s">
+        <v>355</v>
+      </c>
+      <c r="I5" s="154"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A6" s="154"/>
+      <c r="B6" s="154"/>
+      <c r="C6" s="154" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="154" t="s">
+        <v>357</v>
+      </c>
+      <c r="E6" s="154"/>
+      <c r="F6" s="154" t="s">
+        <v>164</v>
+      </c>
+      <c r="G6" s="154" t="s">
+        <v>334</v>
+      </c>
+      <c r="H6" s="154" t="s">
+        <v>355</v>
+      </c>
+      <c r="I6" s="154"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A7" s="154"/>
+      <c r="B7" s="154"/>
+      <c r="C7" s="154" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="154" t="s">
+        <v>358</v>
+      </c>
+      <c r="E7" s="154"/>
+      <c r="F7" s="154" t="s">
+        <v>164</v>
+      </c>
+      <c r="G7" s="154" t="s">
+        <v>330</v>
+      </c>
+      <c r="H7" s="154" t="s">
+        <v>355</v>
+      </c>
+      <c r="I7" s="154"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A8" s="154"/>
+      <c r="B8" s="154"/>
+      <c r="C8" s="154" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="154" t="s">
+        <v>359</v>
+      </c>
+      <c r="E8" s="154"/>
+      <c r="F8" s="154" t="s">
+        <v>164</v>
+      </c>
+      <c r="G8" s="154" t="s">
+        <v>288</v>
+      </c>
+      <c r="H8" s="154" t="s">
+        <v>355</v>
+      </c>
+      <c r="I8" s="154"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:AMJ8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -3406,7 +3696,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:AMJ21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -3692,7 +3982,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:AMJ14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -3974,7 +4264,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:AMJ3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -4064,7 +4354,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:AMJ11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
@@ -4340,7 +4630,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:AMJ14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -4644,7 +4934,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:AMJ7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -4755,89 +5045,6 @@
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{0A785463-FE1F-4E46-B51F-2D8E11E652CC}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.3"/>
-  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:AMJ5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="16" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="2" width="16" style="10"/>
-    <col min="3" max="3" width="20.5" style="10" customWidth="1"/>
-    <col min="4" max="1024" width="16" style="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-    </row>
-    <row r="2" spans="1:6" s="41" customFormat="1" ht="42" x14ac:dyDescent="0.15">
-      <c r="A2" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="73" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="74" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="117" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="73" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="73" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="48"/>
-      <c r="C4" s="25"/>
-    </row>
-    <row r="5" spans="1:6" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="48"/>
-      <c r="C5" s="25"/>
-    </row>
-  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.3"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
@@ -4961,6 +5168,89 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+  <dimension ref="A1:AMJ5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="16" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="2" width="16" style="10"/>
+    <col min="3" max="3" width="20.5" style="10" customWidth="1"/>
+    <col min="4" max="1024" width="16" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+    </row>
+    <row r="2" spans="1:6" s="41" customFormat="1" ht="42" x14ac:dyDescent="0.15">
+      <c r="A2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="73" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="74" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="117" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="73" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="73" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="48"/>
+      <c r="C4" s="25"/>
+    </row>
+    <row r="5" spans="1:6" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="48"/>
+      <c r="C5" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.3"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:AMJ7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -5102,7 +5392,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:AMJ15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -5421,7 +5711,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:AMJ14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -5704,7 +5994,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:AMJ4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -5818,7 +6108,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:AMJ6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -5961,7 +6251,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <sheetPr>
     <tabColor rgb="FFC5E0B4"/>

--- a/src/functionalTest/resources/CCD_HRS_v1.8-AAT.xlsx
+++ b/src/functionalTest/resources/CCD_HRS_v1.8-AAT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mustafadayican/hmcts/em/em-hrs-api/src/functionalTest/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF320B6-D628-954E-8ADC-A5EFC2982C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6663939-5FAD-9C48-B9B1-CE56E365419C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8200" yWindow="660" windowWidth="34560" windowHeight="20380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2080" yWindow="660" windowWidth="34560" windowHeight="20380" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Change History" sheetId="1" r:id="rId1"/>
@@ -18,13 +18,13 @@
     <sheet name="CaseType" sheetId="3" r:id="rId3"/>
     <sheet name="State" sheetId="4" r:id="rId4"/>
     <sheet name="CaseField" sheetId="5" r:id="rId5"/>
-    <sheet name="ComplexTypes" sheetId="6" r:id="rId6"/>
-    <sheet name="FixedLists" sheetId="7" r:id="rId7"/>
-    <sheet name="CaseEvent" sheetId="8" r:id="rId8"/>
-    <sheet name="CaseEventToFields" sheetId="9" r:id="rId9"/>
-    <sheet name="EventToComplexTypes" sheetId="10" r:id="rId10"/>
-    <sheet name="CaseTypeTab" sheetId="11" r:id="rId11"/>
-    <sheet name="RoleToAccessProfiles" sheetId="26" r:id="rId12"/>
+    <sheet name="RoleToAccessProfiles" sheetId="26" r:id="rId6"/>
+    <sheet name="ComplexTypes" sheetId="6" r:id="rId7"/>
+    <sheet name="FixedLists" sheetId="7" r:id="rId8"/>
+    <sheet name="CaseEvent" sheetId="8" r:id="rId9"/>
+    <sheet name="CaseEventToFields" sheetId="9" r:id="rId10"/>
+    <sheet name="EventToComplexTypes" sheetId="10" r:id="rId11"/>
+    <sheet name="CaseTypeTab" sheetId="11" r:id="rId12"/>
     <sheet name="ChallengeQuestion" sheetId="12" r:id="rId13"/>
     <sheet name="SearchInputFields" sheetId="13" r:id="rId14"/>
     <sheet name="SearchResultFields" sheetId="14" r:id="rId15"/>
@@ -2739,6 +2739,1145 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:AMJ36"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="25.33203125" style="10" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="21" style="10" customWidth="1"/>
+    <col min="5" max="5" width="26.5" style="10" customWidth="1"/>
+    <col min="6" max="7" width="29.5" style="10" customWidth="1"/>
+    <col min="8" max="8" width="21.83203125" style="10" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" style="10" customWidth="1"/>
+    <col min="10" max="10" width="24.33203125" style="10" customWidth="1"/>
+    <col min="11" max="11" width="23.1640625" style="10" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" style="10" customWidth="1"/>
+    <col min="13" max="13" width="17.83203125" style="10" customWidth="1"/>
+    <col min="14" max="14" width="19.5" style="10" customWidth="1"/>
+    <col min="15" max="16" width="22" style="10" customWidth="1"/>
+    <col min="17" max="17" width="37" style="10" customWidth="1"/>
+    <col min="18" max="18" width="28.33203125" style="10" customWidth="1"/>
+    <col min="19" max="19" width="24.6640625" style="10" customWidth="1"/>
+    <col min="20" max="20" width="37.6640625" style="10" customWidth="1"/>
+    <col min="21" max="1024" width="8.83203125" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:33" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+    </row>
+    <row r="2" spans="1:33" ht="74.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="O2" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q2" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="R2" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="S2" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="T2" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="U2" s="41"/>
+      <c r="V2" s="41"/>
+      <c r="W2" s="41"/>
+      <c r="X2" s="41"/>
+      <c r="Y2" s="41"/>
+      <c r="Z2" s="41"/>
+      <c r="AA2" s="41"/>
+      <c r="AB2" s="41"/>
+      <c r="AC2" s="41"/>
+      <c r="AD2" s="41"/>
+      <c r="AE2" s="41"/>
+      <c r="AF2" s="41"/>
+      <c r="AG2" s="41"/>
+    </row>
+    <row r="3" spans="1:33" ht="14" x14ac:dyDescent="0.15">
+      <c r="A3" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="E3" s="42" t="s">
+        <v>192</v>
+      </c>
+      <c r="F3" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="G3" s="42" t="s">
+        <v>194</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="I3" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="M3" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="N3" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="O3" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="P3" s="68" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q3" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="R3" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="S3" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="T3" s="20" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="23">
+        <v>44197</v>
+      </c>
+      <c r="B4" s="62"/>
+      <c r="C4" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="E4" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="62">
+        <v>1</v>
+      </c>
+      <c r="I4" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="J4" s="54"/>
+      <c r="K4" s="62" t="s">
+        <v>207</v>
+      </c>
+      <c r="L4" s="45"/>
+      <c r="M4" s="54">
+        <v>1</v>
+      </c>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="45"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="54"/>
+      <c r="T4" s="54"/>
+    </row>
+    <row r="5" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="23">
+        <v>44197</v>
+      </c>
+      <c r="B5" s="62"/>
+      <c r="C5" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="E5" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="62">
+        <v>1</v>
+      </c>
+      <c r="I5" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="J5" s="54"/>
+      <c r="K5" s="62" t="s">
+        <v>207</v>
+      </c>
+      <c r="L5" s="45"/>
+      <c r="M5" s="54">
+        <v>1</v>
+      </c>
+      <c r="N5" s="54"/>
+      <c r="O5" s="54"/>
+      <c r="P5" s="54"/>
+      <c r="Q5" s="45"/>
+      <c r="R5" s="62"/>
+      <c r="S5" s="54"/>
+      <c r="T5" s="54"/>
+    </row>
+    <row r="6" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="23">
+        <v>44197</v>
+      </c>
+      <c r="B6" s="62"/>
+      <c r="C6" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="E6" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="62">
+        <v>1</v>
+      </c>
+      <c r="I6" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="J6" s="54"/>
+      <c r="K6" s="62" t="s">
+        <v>207</v>
+      </c>
+      <c r="L6" s="45"/>
+      <c r="M6" s="54">
+        <v>1</v>
+      </c>
+      <c r="N6" s="54"/>
+      <c r="O6" s="54"/>
+      <c r="P6" s="45"/>
+      <c r="Q6" s="45"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="54"/>
+      <c r="T6" s="54"/>
+    </row>
+    <row r="7" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="23">
+        <v>44197</v>
+      </c>
+      <c r="B7" s="62"/>
+      <c r="C7" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="E7" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="62">
+        <v>1</v>
+      </c>
+      <c r="I7" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="J7" s="54"/>
+      <c r="K7" s="62" t="s">
+        <v>207</v>
+      </c>
+      <c r="L7" s="45"/>
+      <c r="M7" s="54">
+        <v>1</v>
+      </c>
+      <c r="N7" s="54"/>
+      <c r="O7" s="54"/>
+      <c r="P7" s="45"/>
+      <c r="Q7" s="45"/>
+      <c r="R7" s="62"/>
+      <c r="S7" s="54"/>
+      <c r="T7" s="54"/>
+    </row>
+    <row r="8" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="23">
+        <v>44197</v>
+      </c>
+      <c r="B8" s="62"/>
+      <c r="C8" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="E8" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="62">
+        <v>1</v>
+      </c>
+      <c r="I8" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="J8" s="54"/>
+      <c r="K8" s="62" t="s">
+        <v>207</v>
+      </c>
+      <c r="L8" s="45"/>
+      <c r="M8" s="54">
+        <v>1</v>
+      </c>
+      <c r="N8" s="54"/>
+      <c r="O8" s="54"/>
+      <c r="P8" s="54"/>
+      <c r="Q8" s="45"/>
+      <c r="R8" s="62"/>
+      <c r="S8" s="54"/>
+      <c r="T8" s="54"/>
+    </row>
+    <row r="9" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="23">
+        <v>44197</v>
+      </c>
+      <c r="B9" s="62"/>
+      <c r="C9" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="E9" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="62">
+        <v>1</v>
+      </c>
+      <c r="I9" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="J9" s="54"/>
+      <c r="K9" s="62" t="s">
+        <v>207</v>
+      </c>
+      <c r="L9" s="45"/>
+      <c r="M9" s="54">
+        <v>1</v>
+      </c>
+      <c r="N9" s="54"/>
+      <c r="O9" s="54"/>
+      <c r="P9" s="54"/>
+      <c r="Q9" s="45"/>
+      <c r="R9" s="62"/>
+      <c r="S9" s="54"/>
+      <c r="T9" s="54"/>
+    </row>
+    <row r="10" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="23">
+        <v>44197</v>
+      </c>
+      <c r="B10" s="62"/>
+      <c r="C10" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="E10" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="62">
+        <v>1</v>
+      </c>
+      <c r="I10" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="J10" s="54"/>
+      <c r="K10" s="62" t="s">
+        <v>207</v>
+      </c>
+      <c r="L10" s="45"/>
+      <c r="M10" s="54">
+        <v>1</v>
+      </c>
+      <c r="N10" s="54"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="54"/>
+      <c r="Q10" s="45"/>
+      <c r="R10" s="62"/>
+      <c r="S10" s="54"/>
+      <c r="T10" s="54"/>
+    </row>
+    <row r="11" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="23">
+        <v>44197</v>
+      </c>
+      <c r="B11" s="62"/>
+      <c r="C11" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="E11" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="62">
+        <v>1</v>
+      </c>
+      <c r="I11" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="J11" s="54"/>
+      <c r="K11" s="62" t="s">
+        <v>207</v>
+      </c>
+      <c r="L11" s="45"/>
+      <c r="M11" s="54">
+        <v>1</v>
+      </c>
+      <c r="N11" s="54"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="54"/>
+      <c r="Q11" s="45"/>
+      <c r="R11" s="62"/>
+      <c r="S11" s="54"/>
+      <c r="T11" s="54"/>
+    </row>
+    <row r="12" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="23">
+        <v>44197</v>
+      </c>
+      <c r="B12" s="62"/>
+      <c r="C12" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="E12" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="62">
+        <v>1</v>
+      </c>
+      <c r="I12" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="J12" s="54"/>
+      <c r="K12" s="62" t="s">
+        <v>207</v>
+      </c>
+      <c r="L12" s="45"/>
+      <c r="M12" s="54">
+        <v>1</v>
+      </c>
+      <c r="N12" s="54"/>
+      <c r="O12" s="54"/>
+      <c r="P12" s="54"/>
+      <c r="Q12" s="45"/>
+      <c r="R12" s="62"/>
+      <c r="S12" s="54"/>
+      <c r="T12" s="54"/>
+    </row>
+    <row r="13" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="23">
+        <v>44197</v>
+      </c>
+      <c r="B13" s="62"/>
+      <c r="C13" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="E13" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="62">
+        <v>1</v>
+      </c>
+      <c r="I13" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="J13" s="54"/>
+      <c r="K13" s="62" t="s">
+        <v>208</v>
+      </c>
+      <c r="L13" s="45"/>
+      <c r="M13" s="54">
+        <v>2</v>
+      </c>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="45"/>
+      <c r="R13" s="62"/>
+      <c r="S13" s="54"/>
+      <c r="T13" s="54"/>
+    </row>
+    <row r="14" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="23">
+        <v>44197</v>
+      </c>
+      <c r="B14" s="62"/>
+      <c r="C14" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="E14" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="62">
+        <v>1</v>
+      </c>
+      <c r="I14" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="J14" s="54"/>
+      <c r="K14" s="62" t="s">
+        <v>208</v>
+      </c>
+      <c r="L14" s="45"/>
+      <c r="M14" s="54">
+        <v>2</v>
+      </c>
+      <c r="N14" s="54"/>
+      <c r="O14" s="54"/>
+      <c r="P14" s="45"/>
+      <c r="Q14" s="45"/>
+      <c r="R14" s="62"/>
+      <c r="S14" s="54"/>
+      <c r="T14" s="54"/>
+    </row>
+    <row r="15" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="23">
+        <v>44197</v>
+      </c>
+      <c r="B15" s="62"/>
+      <c r="C15" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="E15" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="62">
+        <v>1</v>
+      </c>
+      <c r="I15" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="J15" s="54"/>
+      <c r="K15" s="62" t="s">
+        <v>208</v>
+      </c>
+      <c r="L15" s="45"/>
+      <c r="M15" s="54">
+        <v>2</v>
+      </c>
+      <c r="N15" s="54"/>
+      <c r="O15" s="54"/>
+      <c r="P15" s="54"/>
+      <c r="Q15" s="45"/>
+      <c r="R15" s="62"/>
+      <c r="S15" s="54"/>
+      <c r="T15" s="54"/>
+    </row>
+    <row r="16" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="23">
+        <v>44197</v>
+      </c>
+      <c r="B16" s="62"/>
+      <c r="C16" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="E16" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="62">
+        <v>1</v>
+      </c>
+      <c r="I16" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="J16" s="54"/>
+      <c r="K16" s="62" t="s">
+        <v>208</v>
+      </c>
+      <c r="L16" s="45"/>
+      <c r="M16" s="54">
+        <v>2</v>
+      </c>
+      <c r="N16" s="54"/>
+      <c r="O16" s="54"/>
+      <c r="P16" s="54"/>
+      <c r="Q16" s="45"/>
+      <c r="R16" s="62"/>
+      <c r="S16" s="54"/>
+      <c r="T16" s="54"/>
+    </row>
+    <row r="17" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="23">
+        <v>44197</v>
+      </c>
+      <c r="B17" s="62"/>
+      <c r="C17" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="E17" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="62">
+        <v>1</v>
+      </c>
+      <c r="I17" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="J17" s="54"/>
+      <c r="K17" s="62" t="s">
+        <v>208</v>
+      </c>
+      <c r="L17" s="45"/>
+      <c r="M17" s="54">
+        <v>2</v>
+      </c>
+      <c r="N17" s="54"/>
+      <c r="O17" s="54"/>
+      <c r="P17" s="54"/>
+      <c r="Q17" s="45"/>
+      <c r="R17" s="62"/>
+      <c r="S17" s="54"/>
+      <c r="T17" s="54"/>
+    </row>
+    <row r="18" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="23">
+        <v>44197</v>
+      </c>
+      <c r="B18" s="62"/>
+      <c r="C18" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="62">
+        <v>1</v>
+      </c>
+      <c r="I18" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="J18" s="54"/>
+      <c r="K18" s="62" t="s">
+        <v>208</v>
+      </c>
+      <c r="L18" s="45"/>
+      <c r="M18" s="54">
+        <v>2</v>
+      </c>
+      <c r="N18" s="54"/>
+      <c r="O18" s="54"/>
+      <c r="P18" s="54"/>
+      <c r="Q18" s="45"/>
+      <c r="R18" s="62"/>
+      <c r="S18" s="54"/>
+      <c r="T18" s="54"/>
+    </row>
+    <row r="19" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="23">
+        <v>44197</v>
+      </c>
+      <c r="B19" s="62"/>
+      <c r="C19" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="E19" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="62">
+        <v>1</v>
+      </c>
+      <c r="I19" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="J19" s="54"/>
+      <c r="K19" s="62" t="s">
+        <v>208</v>
+      </c>
+      <c r="L19" s="45"/>
+      <c r="M19" s="54">
+        <v>2</v>
+      </c>
+      <c r="N19" s="54"/>
+      <c r="O19" s="54"/>
+      <c r="P19" s="54"/>
+      <c r="Q19" s="45"/>
+      <c r="R19" s="62"/>
+      <c r="S19" s="54"/>
+      <c r="T19" s="54"/>
+    </row>
+    <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="23">
+        <v>44197</v>
+      </c>
+      <c r="B20" s="62"/>
+      <c r="C20" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="E20" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="62">
+        <v>1</v>
+      </c>
+      <c r="I20" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="J20" s="54"/>
+      <c r="K20" s="62" t="s">
+        <v>208</v>
+      </c>
+      <c r="L20" s="45"/>
+      <c r="M20" s="54">
+        <v>2</v>
+      </c>
+      <c r="N20" s="54"/>
+      <c r="O20" s="54"/>
+      <c r="P20" s="54"/>
+      <c r="Q20" s="45"/>
+      <c r="R20" s="62"/>
+      <c r="S20" s="54"/>
+      <c r="T20" s="54"/>
+    </row>
+    <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="23">
+        <v>44197</v>
+      </c>
+      <c r="B21" s="62"/>
+      <c r="C21" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="E21" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="62">
+        <v>1</v>
+      </c>
+      <c r="I21" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="J21" s="54"/>
+      <c r="K21" s="62" t="s">
+        <v>209</v>
+      </c>
+      <c r="L21" s="45"/>
+      <c r="M21" s="54">
+        <v>2</v>
+      </c>
+      <c r="N21" s="54"/>
+      <c r="O21" s="54"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="45"/>
+      <c r="R21" s="62"/>
+      <c r="S21" s="54"/>
+      <c r="T21" s="54"/>
+    </row>
+    <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="23">
+        <v>44197</v>
+      </c>
+      <c r="B22" s="62"/>
+      <c r="C22" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="E22" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="62">
+        <v>1</v>
+      </c>
+      <c r="I22" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="J22" s="54"/>
+      <c r="K22" s="62" t="s">
+        <v>209</v>
+      </c>
+      <c r="L22" s="45"/>
+      <c r="M22" s="54">
+        <v>3</v>
+      </c>
+      <c r="N22" s="54"/>
+      <c r="O22" s="54"/>
+      <c r="P22" s="54"/>
+      <c r="Q22" s="45"/>
+      <c r="R22" s="62"/>
+      <c r="S22" s="54"/>
+      <c r="T22" s="54"/>
+    </row>
+    <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="23">
+        <v>44197</v>
+      </c>
+      <c r="B23" s="62"/>
+      <c r="C23" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="54" t="s">
+        <v>171</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="62">
+        <v>1</v>
+      </c>
+      <c r="I23" s="71" t="s">
+        <v>210</v>
+      </c>
+      <c r="J23" s="54"/>
+      <c r="K23" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="L23" s="45"/>
+      <c r="M23" s="54">
+        <v>4</v>
+      </c>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="45"/>
+      <c r="R23" s="62"/>
+      <c r="S23" s="54"/>
+      <c r="T23" s="54"/>
+    </row>
+    <row r="24" spans="1:20" ht="14" x14ac:dyDescent="0.15">
+      <c r="A24" s="23">
+        <v>45292</v>
+      </c>
+      <c r="B24" s="62"/>
+      <c r="C24" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="54" t="s">
+        <v>319</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="62">
+        <v>1</v>
+      </c>
+      <c r="I24" s="69" t="s">
+        <v>206</v>
+      </c>
+      <c r="J24" s="54"/>
+      <c r="K24" s="62" t="s">
+        <v>208</v>
+      </c>
+      <c r="L24" s="45"/>
+      <c r="M24" s="54">
+        <v>1</v>
+      </c>
+      <c r="N24" s="54"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="45"/>
+      <c r="R24" s="62"/>
+      <c r="S24" s="54"/>
+      <c r="T24" s="54"/>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.15">
+      <c r="A25" s="48"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
+      <c r="K25" s="56"/>
+      <c r="L25" s="56"/>
+      <c r="Q25" s="56"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.15">
+      <c r="A26" s="48"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="56"/>
+      <c r="K26" s="56"/>
+      <c r="L26" s="56"/>
+      <c r="Q26" s="56"/>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.15">
+      <c r="A27" s="48"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="56"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="56"/>
+      <c r="K27" s="56"/>
+      <c r="L27" s="56"/>
+      <c r="Q27" s="56"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.15">
+      <c r="A28" s="48"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="56"/>
+      <c r="K28" s="56"/>
+      <c r="L28" s="56"/>
+      <c r="Q28" s="56"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.15">
+      <c r="A29" s="48"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="56"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="56"/>
+      <c r="K29" s="56"/>
+      <c r="L29" s="56"/>
+      <c r="Q29" s="56"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.15">
+      <c r="A30" s="48"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="56"/>
+      <c r="K30" s="56"/>
+      <c r="L30" s="56"/>
+      <c r="O30" s="56"/>
+      <c r="P30" s="56"/>
+      <c r="Q30" s="56"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.15">
+      <c r="A31" s="48"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="56"/>
+      <c r="D31" s="56"/>
+      <c r="K31" s="56"/>
+      <c r="L31" s="56"/>
+      <c r="Q31" s="56"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.15">
+      <c r="A32" s="48"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="56"/>
+      <c r="K32" s="56"/>
+      <c r="L32" s="56"/>
+      <c r="Q32" s="56"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A33" s="48"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="56"/>
+      <c r="K33" s="56"/>
+      <c r="L33" s="56"/>
+      <c r="Q33" s="56"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A34" s="48"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="56"/>
+      <c r="G34" s="56"/>
+      <c r="K34" s="56"/>
+      <c r="L34" s="56"/>
+      <c r="Q34" s="56"/>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A35" s="48"/>
+      <c r="B35" s="48"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="72"/>
+      <c r="G35" s="72"/>
+      <c r="K35" s="56"/>
+      <c r="L35" s="56"/>
+      <c r="Q35" s="56"/>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A36" s="48"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="56"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="72"/>
+      <c r="F36" s="72"/>
+      <c r="G36" s="72"/>
+      <c r="K36" s="56"/>
+      <c r="L36" s="56"/>
+      <c r="Q36" s="56"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:AMJ6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -2951,7 +4090,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:AMJ12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -3306,203 +4445,6 @@
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;P</oddFooter>
   </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{403AD85A-BCD6-8B44-A8CA-37608B720DFA}">
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="32.5" customWidth="1"/>
-    <col min="7" max="7" width="44.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="42" x14ac:dyDescent="0.15">
-      <c r="A1" s="151" t="s">
-        <v>341</v>
-      </c>
-      <c r="B1" s="152" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="152" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="152" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="153"/>
-      <c r="F1" s="153"/>
-      <c r="G1" s="153"/>
-      <c r="H1" s="153"/>
-      <c r="I1" s="153"/>
-    </row>
-    <row r="2" spans="1:9" ht="112" x14ac:dyDescent="0.15">
-      <c r="A2" s="152" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="152" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="152" t="s">
-        <v>283</v>
-      </c>
-      <c r="D2" s="152" t="s">
-        <v>342</v>
-      </c>
-      <c r="E2" s="152" t="s">
-        <v>343</v>
-      </c>
-      <c r="F2" s="152" t="s">
-        <v>344</v>
-      </c>
-      <c r="G2" s="152" t="s">
-        <v>345</v>
-      </c>
-      <c r="H2" s="152" t="s">
-        <v>346</v>
-      </c>
-      <c r="I2" s="152" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="42" x14ac:dyDescent="0.15">
-      <c r="A3" s="151" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="151" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="151" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="151" t="s">
-        <v>348</v>
-      </c>
-      <c r="E3" s="151" t="s">
-        <v>349</v>
-      </c>
-      <c r="F3" s="151" t="s">
-        <v>350</v>
-      </c>
-      <c r="G3" s="151" t="s">
-        <v>351</v>
-      </c>
-      <c r="H3" s="151" t="s">
-        <v>352</v>
-      </c>
-      <c r="I3" s="151" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A4" s="154"/>
-      <c r="B4" s="154"/>
-      <c r="C4" s="154" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="154" t="s">
-        <v>354</v>
-      </c>
-      <c r="E4" s="154"/>
-      <c r="F4" s="154" t="s">
-        <v>164</v>
-      </c>
-      <c r="G4" s="154" t="s">
-        <v>287</v>
-      </c>
-      <c r="H4" s="154" t="s">
-        <v>355</v>
-      </c>
-      <c r="I4" s="154"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A5" s="154"/>
-      <c r="B5" s="154"/>
-      <c r="C5" s="154" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="154" t="s">
-        <v>356</v>
-      </c>
-      <c r="E5" s="154"/>
-      <c r="F5" s="154" t="s">
-        <v>164</v>
-      </c>
-      <c r="G5" s="154" t="s">
-        <v>288</v>
-      </c>
-      <c r="H5" s="154" t="s">
-        <v>355</v>
-      </c>
-      <c r="I5" s="154"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A6" s="154"/>
-      <c r="B6" s="154"/>
-      <c r="C6" s="154" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="154" t="s">
-        <v>357</v>
-      </c>
-      <c r="E6" s="154"/>
-      <c r="F6" s="154" t="s">
-        <v>164</v>
-      </c>
-      <c r="G6" s="154" t="s">
-        <v>334</v>
-      </c>
-      <c r="H6" s="154" t="s">
-        <v>355</v>
-      </c>
-      <c r="I6" s="154"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A7" s="154"/>
-      <c r="B7" s="154"/>
-      <c r="C7" s="154" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="154" t="s">
-        <v>358</v>
-      </c>
-      <c r="E7" s="154"/>
-      <c r="F7" s="154" t="s">
-        <v>164</v>
-      </c>
-      <c r="G7" s="154" t="s">
-        <v>330</v>
-      </c>
-      <c r="H7" s="154" t="s">
-        <v>355</v>
-      </c>
-      <c r="I7" s="154"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A8" s="154"/>
-      <c r="B8" s="154"/>
-      <c r="C8" s="154" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="154" t="s">
-        <v>359</v>
-      </c>
-      <c r="E8" s="154"/>
-      <c r="F8" s="154" t="s">
-        <v>164</v>
-      </c>
-      <c r="G8" s="154" t="s">
-        <v>288</v>
-      </c>
-      <c r="H8" s="154" t="s">
-        <v>355</v>
-      </c>
-      <c r="I8" s="154"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -10215,6 +11157,203 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{403AD85A-BCD6-8B44-A8CA-37608B720DFA}">
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="3" max="3" width="33" customWidth="1"/>
+    <col min="4" max="4" width="32.5" customWidth="1"/>
+    <col min="7" max="7" width="44.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="42" x14ac:dyDescent="0.15">
+      <c r="A1" s="151" t="s">
+        <v>341</v>
+      </c>
+      <c r="B1" s="152" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="152" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="152" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="153"/>
+      <c r="F1" s="153"/>
+      <c r="G1" s="153"/>
+      <c r="H1" s="153"/>
+      <c r="I1" s="153"/>
+    </row>
+    <row r="2" spans="1:9" ht="112" x14ac:dyDescent="0.15">
+      <c r="A2" s="152" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="152" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="152" t="s">
+        <v>283</v>
+      </c>
+      <c r="D2" s="152" t="s">
+        <v>342</v>
+      </c>
+      <c r="E2" s="152" t="s">
+        <v>343</v>
+      </c>
+      <c r="F2" s="152" t="s">
+        <v>344</v>
+      </c>
+      <c r="G2" s="152" t="s">
+        <v>345</v>
+      </c>
+      <c r="H2" s="152" t="s">
+        <v>346</v>
+      </c>
+      <c r="I2" s="152" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="42" x14ac:dyDescent="0.15">
+      <c r="A3" s="151" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="151" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="151" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="151" t="s">
+        <v>348</v>
+      </c>
+      <c r="E3" s="151" t="s">
+        <v>349</v>
+      </c>
+      <c r="F3" s="151" t="s">
+        <v>350</v>
+      </c>
+      <c r="G3" s="151" t="s">
+        <v>351</v>
+      </c>
+      <c r="H3" s="151" t="s">
+        <v>352</v>
+      </c>
+      <c r="I3" s="151" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A4" s="154"/>
+      <c r="B4" s="154"/>
+      <c r="C4" s="154" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="154" t="s">
+        <v>354</v>
+      </c>
+      <c r="E4" s="154"/>
+      <c r="F4" s="154" t="s">
+        <v>164</v>
+      </c>
+      <c r="G4" s="154" t="s">
+        <v>287</v>
+      </c>
+      <c r="H4" s="154" t="s">
+        <v>355</v>
+      </c>
+      <c r="I4" s="154"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A5" s="154"/>
+      <c r="B5" s="154"/>
+      <c r="C5" s="154" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="154" t="s">
+        <v>356</v>
+      </c>
+      <c r="E5" s="154"/>
+      <c r="F5" s="154" t="s">
+        <v>164</v>
+      </c>
+      <c r="G5" s="154" t="s">
+        <v>288</v>
+      </c>
+      <c r="H5" s="154" t="s">
+        <v>355</v>
+      </c>
+      <c r="I5" s="154"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A6" s="154"/>
+      <c r="B6" s="154"/>
+      <c r="C6" s="154" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="154" t="s">
+        <v>357</v>
+      </c>
+      <c r="E6" s="154"/>
+      <c r="F6" s="154" t="s">
+        <v>164</v>
+      </c>
+      <c r="G6" s="154" t="s">
+        <v>334</v>
+      </c>
+      <c r="H6" s="154" t="s">
+        <v>355</v>
+      </c>
+      <c r="I6" s="154"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A7" s="154"/>
+      <c r="B7" s="154"/>
+      <c r="C7" s="154" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="154" t="s">
+        <v>358</v>
+      </c>
+      <c r="E7" s="154"/>
+      <c r="F7" s="154" t="s">
+        <v>164</v>
+      </c>
+      <c r="G7" s="154" t="s">
+        <v>330</v>
+      </c>
+      <c r="H7" s="154" t="s">
+        <v>355</v>
+      </c>
+      <c r="I7" s="154"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A8" s="154"/>
+      <c r="B8" s="154"/>
+      <c r="C8" s="154" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="154" t="s">
+        <v>359</v>
+      </c>
+      <c r="E8" s="154"/>
+      <c r="F8" s="154" t="s">
+        <v>164</v>
+      </c>
+      <c r="G8" s="154" t="s">
+        <v>288</v>
+      </c>
+      <c r="H8" s="154" t="s">
+        <v>355</v>
+      </c>
+      <c r="I8" s="154"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AMJ18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -11014,7 +12153,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AMJ5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -11136,7 +12275,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AMI9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -11593,1145 +12732,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:AMJ36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="25.33203125" style="10" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="21" style="10" customWidth="1"/>
-    <col min="5" max="5" width="26.5" style="10" customWidth="1"/>
-    <col min="6" max="7" width="29.5" style="10" customWidth="1"/>
-    <col min="8" max="8" width="21.83203125" style="10" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" style="10" customWidth="1"/>
-    <col min="10" max="10" width="24.33203125" style="10" customWidth="1"/>
-    <col min="11" max="11" width="23.1640625" style="10" customWidth="1"/>
-    <col min="12" max="12" width="16.33203125" style="10" customWidth="1"/>
-    <col min="13" max="13" width="17.83203125" style="10" customWidth="1"/>
-    <col min="14" max="14" width="19.5" style="10" customWidth="1"/>
-    <col min="15" max="16" width="22" style="10" customWidth="1"/>
-    <col min="17" max="17" width="37" style="10" customWidth="1"/>
-    <col min="18" max="18" width="28.33203125" style="10" customWidth="1"/>
-    <col min="19" max="19" width="24.6640625" style="10" customWidth="1"/>
-    <col min="20" max="20" width="37.6640625" style="10" customWidth="1"/>
-    <col min="21" max="1024" width="8.83203125" style="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:33" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-    </row>
-    <row r="2" spans="1:33" ht="74.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="K2" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="M2" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="N2" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="O2" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q2" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="R2" s="15" t="s">
-        <v>190</v>
-      </c>
-      <c r="S2" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="T2" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="41"/>
-      <c r="Y2" s="41"/>
-      <c r="Z2" s="41"/>
-      <c r="AA2" s="41"/>
-      <c r="AB2" s="41"/>
-      <c r="AC2" s="41"/>
-      <c r="AD2" s="41"/>
-      <c r="AE2" s="41"/>
-      <c r="AF2" s="41"/>
-      <c r="AG2" s="41"/>
-    </row>
-    <row r="3" spans="1:33" ht="14" x14ac:dyDescent="0.15">
-      <c r="A3" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="42" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>192</v>
-      </c>
-      <c r="F3" s="42" t="s">
-        <v>193</v>
-      </c>
-      <c r="G3" s="42" t="s">
-        <v>194</v>
-      </c>
-      <c r="H3" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="I3" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="J3" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="K3" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="L3" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="M3" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="N3" s="20" t="s">
-        <v>200</v>
-      </c>
-      <c r="O3" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="P3" s="68" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q3" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="R3" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="S3" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="T3" s="20" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="23">
-        <v>44197</v>
-      </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="E4" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="62">
-        <v>1</v>
-      </c>
-      <c r="I4" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="J4" s="54"/>
-      <c r="K4" s="62" t="s">
-        <v>207</v>
-      </c>
-      <c r="L4" s="45"/>
-      <c r="M4" s="54">
-        <v>1</v>
-      </c>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="45"/>
-      <c r="R4" s="62"/>
-      <c r="S4" s="54"/>
-      <c r="T4" s="54"/>
-    </row>
-    <row r="5" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="23">
-        <v>44197</v>
-      </c>
-      <c r="B5" s="62"/>
-      <c r="C5" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="E5" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="62">
-        <v>1</v>
-      </c>
-      <c r="I5" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="J5" s="54"/>
-      <c r="K5" s="62" t="s">
-        <v>207</v>
-      </c>
-      <c r="L5" s="45"/>
-      <c r="M5" s="54">
-        <v>1</v>
-      </c>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="54"/>
-      <c r="Q5" s="45"/>
-      <c r="R5" s="62"/>
-      <c r="S5" s="54"/>
-      <c r="T5" s="54"/>
-    </row>
-    <row r="6" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="23">
-        <v>44197</v>
-      </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="E6" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="62">
-        <v>1</v>
-      </c>
-      <c r="I6" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="J6" s="54"/>
-      <c r="K6" s="62" t="s">
-        <v>207</v>
-      </c>
-      <c r="L6" s="45"/>
-      <c r="M6" s="54">
-        <v>1</v>
-      </c>
-      <c r="N6" s="54"/>
-      <c r="O6" s="54"/>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="45"/>
-      <c r="R6" s="62"/>
-      <c r="S6" s="54"/>
-      <c r="T6" s="54"/>
-    </row>
-    <row r="7" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="23">
-        <v>44197</v>
-      </c>
-      <c r="B7" s="62"/>
-      <c r="C7" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="E7" s="46" t="s">
-        <v>92</v>
-      </c>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="62">
-        <v>1</v>
-      </c>
-      <c r="I7" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="J7" s="54"/>
-      <c r="K7" s="62" t="s">
-        <v>207</v>
-      </c>
-      <c r="L7" s="45"/>
-      <c r="M7" s="54">
-        <v>1</v>
-      </c>
-      <c r="N7" s="54"/>
-      <c r="O7" s="54"/>
-      <c r="P7" s="45"/>
-      <c r="Q7" s="45"/>
-      <c r="R7" s="62"/>
-      <c r="S7" s="54"/>
-      <c r="T7" s="54"/>
-    </row>
-    <row r="8" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="23">
-        <v>44197</v>
-      </c>
-      <c r="B8" s="62"/>
-      <c r="C8" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="E8" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="62">
-        <v>1</v>
-      </c>
-      <c r="I8" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="J8" s="54"/>
-      <c r="K8" s="62" t="s">
-        <v>207</v>
-      </c>
-      <c r="L8" s="45"/>
-      <c r="M8" s="54">
-        <v>1</v>
-      </c>
-      <c r="N8" s="54"/>
-      <c r="O8" s="54"/>
-      <c r="P8" s="54"/>
-      <c r="Q8" s="45"/>
-      <c r="R8" s="62"/>
-      <c r="S8" s="54"/>
-      <c r="T8" s="54"/>
-    </row>
-    <row r="9" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="23">
-        <v>44197</v>
-      </c>
-      <c r="B9" s="62"/>
-      <c r="C9" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="E9" s="46" t="s">
-        <v>96</v>
-      </c>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="62">
-        <v>1</v>
-      </c>
-      <c r="I9" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="J9" s="54"/>
-      <c r="K9" s="62" t="s">
-        <v>207</v>
-      </c>
-      <c r="L9" s="45"/>
-      <c r="M9" s="54">
-        <v>1</v>
-      </c>
-      <c r="N9" s="54"/>
-      <c r="O9" s="54"/>
-      <c r="P9" s="54"/>
-      <c r="Q9" s="45"/>
-      <c r="R9" s="62"/>
-      <c r="S9" s="54"/>
-      <c r="T9" s="54"/>
-    </row>
-    <row r="10" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="23">
-        <v>44197</v>
-      </c>
-      <c r="B10" s="62"/>
-      <c r="C10" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="E10" s="46" t="s">
-        <v>98</v>
-      </c>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="62">
-        <v>1</v>
-      </c>
-      <c r="I10" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="J10" s="54"/>
-      <c r="K10" s="62" t="s">
-        <v>207</v>
-      </c>
-      <c r="L10" s="45"/>
-      <c r="M10" s="54">
-        <v>1</v>
-      </c>
-      <c r="N10" s="54"/>
-      <c r="O10" s="54"/>
-      <c r="P10" s="54"/>
-      <c r="Q10" s="45"/>
-      <c r="R10" s="62"/>
-      <c r="S10" s="54"/>
-      <c r="T10" s="54"/>
-    </row>
-    <row r="11" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="23">
-        <v>44197</v>
-      </c>
-      <c r="B11" s="62"/>
-      <c r="C11" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="E11" s="46" t="s">
-        <v>100</v>
-      </c>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="62">
-        <v>1</v>
-      </c>
-      <c r="I11" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="J11" s="54"/>
-      <c r="K11" s="62" t="s">
-        <v>207</v>
-      </c>
-      <c r="L11" s="45"/>
-      <c r="M11" s="54">
-        <v>1</v>
-      </c>
-      <c r="N11" s="54"/>
-      <c r="O11" s="54"/>
-      <c r="P11" s="54"/>
-      <c r="Q11" s="45"/>
-      <c r="R11" s="62"/>
-      <c r="S11" s="54"/>
-      <c r="T11" s="54"/>
-    </row>
-    <row r="12" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="23">
-        <v>44197</v>
-      </c>
-      <c r="B12" s="62"/>
-      <c r="C12" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="E12" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="62">
-        <v>1</v>
-      </c>
-      <c r="I12" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="J12" s="54"/>
-      <c r="K12" s="62" t="s">
-        <v>207</v>
-      </c>
-      <c r="L12" s="45"/>
-      <c r="M12" s="54">
-        <v>1</v>
-      </c>
-      <c r="N12" s="54"/>
-      <c r="O12" s="54"/>
-      <c r="P12" s="54"/>
-      <c r="Q12" s="45"/>
-      <c r="R12" s="62"/>
-      <c r="S12" s="54"/>
-      <c r="T12" s="54"/>
-    </row>
-    <row r="13" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="23">
-        <v>44197</v>
-      </c>
-      <c r="B13" s="62"/>
-      <c r="C13" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="E13" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="62">
-        <v>1</v>
-      </c>
-      <c r="I13" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="J13" s="54"/>
-      <c r="K13" s="62" t="s">
-        <v>208</v>
-      </c>
-      <c r="L13" s="45"/>
-      <c r="M13" s="54">
-        <v>2</v>
-      </c>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="45"/>
-      <c r="R13" s="62"/>
-      <c r="S13" s="54"/>
-      <c r="T13" s="54"/>
-    </row>
-    <row r="14" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="23">
-        <v>44197</v>
-      </c>
-      <c r="B14" s="62"/>
-      <c r="C14" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="E14" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="62">
-        <v>1</v>
-      </c>
-      <c r="I14" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="J14" s="54"/>
-      <c r="K14" s="62" t="s">
-        <v>208</v>
-      </c>
-      <c r="L14" s="45"/>
-      <c r="M14" s="54">
-        <v>2</v>
-      </c>
-      <c r="N14" s="54"/>
-      <c r="O14" s="54"/>
-      <c r="P14" s="45"/>
-      <c r="Q14" s="45"/>
-      <c r="R14" s="62"/>
-      <c r="S14" s="54"/>
-      <c r="T14" s="54"/>
-    </row>
-    <row r="15" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="23">
-        <v>44197</v>
-      </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="E15" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="62">
-        <v>1</v>
-      </c>
-      <c r="I15" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="J15" s="54"/>
-      <c r="K15" s="62" t="s">
-        <v>208</v>
-      </c>
-      <c r="L15" s="45"/>
-      <c r="M15" s="54">
-        <v>2</v>
-      </c>
-      <c r="N15" s="54"/>
-      <c r="O15" s="54"/>
-      <c r="P15" s="54"/>
-      <c r="Q15" s="45"/>
-      <c r="R15" s="62"/>
-      <c r="S15" s="54"/>
-      <c r="T15" s="54"/>
-    </row>
-    <row r="16" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="23">
-        <v>44197</v>
-      </c>
-      <c r="B16" s="62"/>
-      <c r="C16" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="E16" s="46" t="s">
-        <v>89</v>
-      </c>
-      <c r="F16" s="45"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="62">
-        <v>1</v>
-      </c>
-      <c r="I16" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="J16" s="54"/>
-      <c r="K16" s="62" t="s">
-        <v>208</v>
-      </c>
-      <c r="L16" s="45"/>
-      <c r="M16" s="54">
-        <v>2</v>
-      </c>
-      <c r="N16" s="54"/>
-      <c r="O16" s="54"/>
-      <c r="P16" s="54"/>
-      <c r="Q16" s="45"/>
-      <c r="R16" s="62"/>
-      <c r="S16" s="54"/>
-      <c r="T16" s="54"/>
-    </row>
-    <row r="17" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="23">
-        <v>44197</v>
-      </c>
-      <c r="B17" s="62"/>
-      <c r="C17" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="E17" s="46" t="s">
-        <v>92</v>
-      </c>
-      <c r="F17" s="45"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="62">
-        <v>1</v>
-      </c>
-      <c r="I17" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="J17" s="54"/>
-      <c r="K17" s="62" t="s">
-        <v>208</v>
-      </c>
-      <c r="L17" s="45"/>
-      <c r="M17" s="54">
-        <v>2</v>
-      </c>
-      <c r="N17" s="54"/>
-      <c r="O17" s="54"/>
-      <c r="P17" s="54"/>
-      <c r="Q17" s="45"/>
-      <c r="R17" s="62"/>
-      <c r="S17" s="54"/>
-      <c r="T17" s="54"/>
-    </row>
-    <row r="18" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="23">
-        <v>44197</v>
-      </c>
-      <c r="B18" s="62"/>
-      <c r="C18" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="E18" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="F18" s="45"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="62">
-        <v>1</v>
-      </c>
-      <c r="I18" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="J18" s="54"/>
-      <c r="K18" s="62" t="s">
-        <v>208</v>
-      </c>
-      <c r="L18" s="45"/>
-      <c r="M18" s="54">
-        <v>2</v>
-      </c>
-      <c r="N18" s="54"/>
-      <c r="O18" s="54"/>
-      <c r="P18" s="54"/>
-      <c r="Q18" s="45"/>
-      <c r="R18" s="62"/>
-      <c r="S18" s="54"/>
-      <c r="T18" s="54"/>
-    </row>
-    <row r="19" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="23">
-        <v>44197</v>
-      </c>
-      <c r="B19" s="62"/>
-      <c r="C19" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="E19" s="46" t="s">
-        <v>96</v>
-      </c>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="62">
-        <v>1</v>
-      </c>
-      <c r="I19" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="J19" s="54"/>
-      <c r="K19" s="62" t="s">
-        <v>208</v>
-      </c>
-      <c r="L19" s="45"/>
-      <c r="M19" s="54">
-        <v>2</v>
-      </c>
-      <c r="N19" s="54"/>
-      <c r="O19" s="54"/>
-      <c r="P19" s="54"/>
-      <c r="Q19" s="45"/>
-      <c r="R19" s="62"/>
-      <c r="S19" s="54"/>
-      <c r="T19" s="54"/>
-    </row>
-    <row r="20" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="23">
-        <v>44197</v>
-      </c>
-      <c r="B20" s="62"/>
-      <c r="C20" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="E20" s="46" t="s">
-        <v>98</v>
-      </c>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="62">
-        <v>1</v>
-      </c>
-      <c r="I20" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="J20" s="54"/>
-      <c r="K20" s="62" t="s">
-        <v>208</v>
-      </c>
-      <c r="L20" s="45"/>
-      <c r="M20" s="54">
-        <v>2</v>
-      </c>
-      <c r="N20" s="54"/>
-      <c r="O20" s="54"/>
-      <c r="P20" s="54"/>
-      <c r="Q20" s="45"/>
-      <c r="R20" s="62"/>
-      <c r="S20" s="54"/>
-      <c r="T20" s="54"/>
-    </row>
-    <row r="21" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="23">
-        <v>44197</v>
-      </c>
-      <c r="B21" s="62"/>
-      <c r="C21" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="E21" s="46" t="s">
-        <v>100</v>
-      </c>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="62">
-        <v>1</v>
-      </c>
-      <c r="I21" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="J21" s="54"/>
-      <c r="K21" s="62" t="s">
-        <v>209</v>
-      </c>
-      <c r="L21" s="45"/>
-      <c r="M21" s="54">
-        <v>2</v>
-      </c>
-      <c r="N21" s="54"/>
-      <c r="O21" s="54"/>
-      <c r="P21" s="54"/>
-      <c r="Q21" s="45"/>
-      <c r="R21" s="62"/>
-      <c r="S21" s="54"/>
-      <c r="T21" s="54"/>
-    </row>
-    <row r="22" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="23">
-        <v>44197</v>
-      </c>
-      <c r="B22" s="62"/>
-      <c r="C22" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="E22" s="46" t="s">
-        <v>100</v>
-      </c>
-      <c r="F22" s="45"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="62">
-        <v>1</v>
-      </c>
-      <c r="I22" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="J22" s="54"/>
-      <c r="K22" s="62" t="s">
-        <v>209</v>
-      </c>
-      <c r="L22" s="45"/>
-      <c r="M22" s="54">
-        <v>3</v>
-      </c>
-      <c r="N22" s="54"/>
-      <c r="O22" s="54"/>
-      <c r="P22" s="54"/>
-      <c r="Q22" s="45"/>
-      <c r="R22" s="62"/>
-      <c r="S22" s="54"/>
-      <c r="T22" s="54"/>
-    </row>
-    <row r="23" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="23">
-        <v>44197</v>
-      </c>
-      <c r="B23" s="62"/>
-      <c r="C23" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="54" t="s">
-        <v>171</v>
-      </c>
-      <c r="E23" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="62">
-        <v>1</v>
-      </c>
-      <c r="I23" s="71" t="s">
-        <v>210</v>
-      </c>
-      <c r="J23" s="54"/>
-      <c r="K23" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="L23" s="45"/>
-      <c r="M23" s="54">
-        <v>4</v>
-      </c>
-      <c r="N23" s="54"/>
-      <c r="O23" s="54"/>
-      <c r="P23" s="54"/>
-      <c r="Q23" s="45"/>
-      <c r="R23" s="62"/>
-      <c r="S23" s="54"/>
-      <c r="T23" s="54"/>
-    </row>
-    <row r="24" spans="1:20" ht="14" x14ac:dyDescent="0.15">
-      <c r="A24" s="23">
-        <v>45292</v>
-      </c>
-      <c r="B24" s="62"/>
-      <c r="C24" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="54" t="s">
-        <v>319</v>
-      </c>
-      <c r="E24" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="F24" s="45"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="62">
-        <v>1</v>
-      </c>
-      <c r="I24" s="69" t="s">
-        <v>206</v>
-      </c>
-      <c r="J24" s="54"/>
-      <c r="K24" s="62" t="s">
-        <v>208</v>
-      </c>
-      <c r="L24" s="45"/>
-      <c r="M24" s="54">
-        <v>1</v>
-      </c>
-      <c r="N24" s="54"/>
-      <c r="O24" s="54"/>
-      <c r="P24" s="54"/>
-      <c r="Q24" s="45"/>
-      <c r="R24" s="62"/>
-      <c r="S24" s="54"/>
-      <c r="T24" s="54"/>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A25" s="48"/>
-      <c r="B25" s="48"/>
-      <c r="C25" s="56"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="56"/>
-      <c r="K25" s="56"/>
-      <c r="L25" s="56"/>
-      <c r="Q25" s="56"/>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="56"/>
-      <c r="K26" s="56"/>
-      <c r="L26" s="56"/>
-      <c r="Q26" s="56"/>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A27" s="48"/>
-      <c r="B27" s="48"/>
-      <c r="C27" s="56"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="56"/>
-      <c r="K27" s="56"/>
-      <c r="L27" s="56"/>
-      <c r="Q27" s="56"/>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A28" s="48"/>
-      <c r="B28" s="48"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="56"/>
-      <c r="Q28" s="56"/>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A29" s="48"/>
-      <c r="B29" s="48"/>
-      <c r="C29" s="56"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="56"/>
-      <c r="K29" s="56"/>
-      <c r="L29" s="56"/>
-      <c r="Q29" s="56"/>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A30" s="48"/>
-      <c r="B30" s="48"/>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
-      <c r="K30" s="56"/>
-      <c r="L30" s="56"/>
-      <c r="O30" s="56"/>
-      <c r="P30" s="56"/>
-      <c r="Q30" s="56"/>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A31" s="48"/>
-      <c r="B31" s="48"/>
-      <c r="C31" s="56"/>
-      <c r="D31" s="56"/>
-      <c r="K31" s="56"/>
-      <c r="L31" s="56"/>
-      <c r="Q31" s="56"/>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A32" s="48"/>
-      <c r="B32" s="48"/>
-      <c r="C32" s="56"/>
-      <c r="D32" s="56"/>
-      <c r="K32" s="56"/>
-      <c r="L32" s="56"/>
-      <c r="Q32" s="56"/>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A33" s="48"/>
-      <c r="B33" s="48"/>
-      <c r="C33" s="56"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="56"/>
-      <c r="G33" s="56"/>
-      <c r="K33" s="56"/>
-      <c r="L33" s="56"/>
-      <c r="Q33" s="56"/>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A34" s="48"/>
-      <c r="B34" s="48"/>
-      <c r="C34" s="56"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="56"/>
-      <c r="G34" s="56"/>
-      <c r="K34" s="56"/>
-      <c r="L34" s="56"/>
-      <c r="Q34" s="56"/>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A35" s="48"/>
-      <c r="B35" s="48"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="72"/>
-      <c r="K35" s="56"/>
-      <c r="L35" s="56"/>
-      <c r="Q35" s="56"/>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A36" s="48"/>
-      <c r="B36" s="48"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="E36" s="72"/>
-      <c r="F36" s="72"/>
-      <c r="G36" s="72"/>
-      <c r="K36" s="56"/>
-      <c r="L36" s="56"/>
-      <c r="Q36" s="56"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{6be7ebee-5b98-4973-86ef-ae3752ea54e7}" enabled="1" method="Privileged" siteId="{b9fec68c-c92d-461e-9a97-3d03a0f18b82}" contentBits="0" removed="0"/>
